--- a/data/trans_bre/IP16B08-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16B08-Clase-trans_bre.xlsx
@@ -879,7 +879,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,04</t>
+          <t>0,0; 41,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 88,82</t>
+          <t>0,0; 72,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,12</t>
+          <t>0,0; 18,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,0</t>
+          <t>0,0; 31,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,64</t>
+          <t>0,0; 22,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,84</t>
+          <t>0,0; 46,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">

--- a/data/trans_bre/IP16B08-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16B08-Clase-trans_bre.xlsx
@@ -879,7 +879,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,81</t>
+          <t>0,0; 46,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,17</t>
+          <t>0,0; 86,95</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,49</t>
+          <t>0,0; 20,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,46</t>
+          <t>0,0; 31,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,68</t>
+          <t>0,0; 25,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,11</t>
+          <t>0,0; 45,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
